--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.04810476116761</v>
+        <v>7.482817023689738</v>
       </c>
       <c r="D2" t="n">
-        <v>44.44250721205488</v>
+        <v>7.221907421958919</v>
       </c>
       <c r="E2" t="n">
-        <v>19.22053429542033</v>
+        <v>3.123336823005803</v>
       </c>
       <c r="F2" t="n">
-        <v>21.78545061751784</v>
+        <v>3.540135725346648</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.03034234400878</v>
+        <v>5.204930630901427</v>
       </c>
       <c r="D3" t="n">
-        <v>7.851240367524228</v>
+        <v>1.275826559722687</v>
       </c>
       <c r="E3" t="n">
-        <v>19.22053429542033</v>
+        <v>3.123336823005803</v>
       </c>
       <c r="F3" t="n">
-        <v>21.78545061751784</v>
+        <v>3.540135725346648</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.00297608503474</v>
+        <v>6.825483613818145</v>
       </c>
       <c r="D4" t="n">
-        <v>56.09615338717612</v>
+        <v>9.115624925416119</v>
       </c>
       <c r="E4" t="n">
-        <v>19.22053429542033</v>
+        <v>3.123336823005803</v>
       </c>
       <c r="F4" t="n">
-        <v>21.78545061751784</v>
+        <v>3.540135725346648</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>77.02515171797522</v>
+        <v>12.51658715417097</v>
       </c>
       <c r="D5" t="n">
-        <v>72.70583155081557</v>
+        <v>11.81469762700753</v>
       </c>
       <c r="E5" t="n">
-        <v>19.22053429542033</v>
+        <v>3.123336823005803</v>
       </c>
       <c r="F5" t="n">
-        <v>21.78545061751784</v>
+        <v>3.540135725346648</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.35172975329193</v>
+        <v>3.144656084909939</v>
       </c>
       <c r="D6" t="n">
-        <v>56.57938469739056</v>
+        <v>9.194150013325967</v>
       </c>
       <c r="E6" t="n">
-        <v>19.22053429542033</v>
+        <v>3.123336823005803</v>
       </c>
       <c r="F6" t="n">
-        <v>21.78545061751784</v>
+        <v>3.540135725346648</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
